--- a/ข้อ2.xlsx
+++ b/ข้อ2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Product_AMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B63713A-FC6B-4A7D-94DF-395DB604519F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39A3B97-BCDD-4BCE-9567-309F7EDD1B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E6D1783-A657-4040-8780-286ED815531D}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3E6D1783-A657-4040-8780-286ED815531D}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="37">
   <si>
     <t>เดือน</t>
   </si>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>ว่างงาน</t>
+  </si>
+  <si>
+    <t>ค่าว่างงาน</t>
+  </si>
+  <si>
+    <t>ค่าของ</t>
   </si>
 </sst>
 </file>
@@ -524,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13E4804-BD06-4C6C-BF26-5931CE160AEA}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.59765625" bestFit="1" customWidth="1"/>
@@ -631,7 +637,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>50</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -661,7 +667,7 @@
       </c>
       <c r="B8">
         <f>IF(B7&gt;$B$6, B7-$B$6, 0)</f>
-        <v>550</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <f>IF(C7&gt;B7, C7-B7, 0)</f>
@@ -718,110 +724,177 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11">
+        <f>IF(B7&gt;B4, 0, B4-B7)</f>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f>IF(C7&gt;C4, 0, C4-C7)</f>
+        <v>300</v>
+      </c>
+      <c r="D11">
+        <f>IF(D7&gt;D4, 0, D4-D7)</f>
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <f>IF(E7&gt;E4, 0, E4-E7)</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
+        <f>IF(B$7&gt;B$4,(B7-B4),0)</f>
+        <v>140</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ref="C12:E12" si="5">IF(C$7&gt;C$4,(C7-C4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13">
+        <f>(B3*0.5)*1600</f>
+        <v>32000</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:E13" si="6">(C3*0.5)*1600</f>
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>SUM(B13:E13)</f>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
+      <c r="B14">
         <f>IF(B$7&gt;B$4,B$4*40*100,B$7*40*100)</f>
         <v>1840000</v>
       </c>
-      <c r="C12">
-        <f t="shared" ref="C12:E12" si="5">IF(C$7&gt;C$4,C$4*40*100,C$7*40*100)</f>
+      <c r="C14">
+        <f t="shared" ref="C14:E14" si="7">IF(C$7&gt;C$4,C$4*40*100,C$7*40*100)</f>
         <v>2400000</v>
       </c>
-      <c r="D12">
-        <f t="shared" si="5"/>
+      <c r="D14">
+        <f t="shared" si="7"/>
         <v>2400000</v>
       </c>
-      <c r="E12">
-        <f t="shared" si="5"/>
+      <c r="E14">
+        <f t="shared" si="7"/>
         <v>1200000</v>
       </c>
-      <c r="F12">
-        <f>SUM(B12:E12)</f>
+      <c r="F14">
+        <f>SUM(B14:E14)</f>
         <v>7840000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13">
-        <f>IF(B$7&gt;B$4,0,(B$4-B$7)*60*100)</f>
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <f t="shared" ref="C13:E13" si="6">IF(C$7&gt;C$4,0,(C$4-C$7)*60*100)</f>
-        <v>1800000</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="6"/>
-        <v>600000</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <f t="shared" ref="F13:F14" si="7">SUM(B13:E13)</f>
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14">
-        <f>IF(B$7&gt;B$4,(B7-B4)*30*100,0)</f>
-        <v>420000</v>
-      </c>
-      <c r="C14">
-        <f t="shared" ref="C14:E14" si="8">IF(C$7&gt;C$4,(C7-C4)*30*100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="8"/>
-        <v>900000</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="7"/>
-        <v>1320000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <f>B11*100*60</f>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:E15" si="8">C11*100*60</f>
+        <v>1800000</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="8"/>
+        <v>600000</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" ref="F15:F16" si="9">SUM(B15:E15)</f>
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <f>B12*30*100</f>
+        <v>420000</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ref="C16:E16" si="10">C12*30*100</f>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="10"/>
+        <v>900000</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="9"/>
+        <v>1320000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>33</v>
       </c>
-      <c r="B15">
+      <c r="B17">
         <f>B8*1000</f>
-        <v>550000</v>
-      </c>
-      <c r="C15">
+        <v>100000</v>
+      </c>
+      <c r="C17">
         <f>C8*2000</f>
         <v>0</v>
       </c>
-      <c r="D15">
+      <c r="D17">
         <f>D8*2000</f>
         <v>0</v>
       </c>
-      <c r="E15">
+      <c r="E17">
         <f>E8*2000</f>
         <v>0</v>
       </c>
-      <c r="F15">
-        <f>SUM(B15:E15)</f>
-        <v>550000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F16">
-        <f>SUM(F12:F15)</f>
-        <v>12110000</v>
+      <c r="F17">
+        <f>SUM(B17:E17)</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <f>SUM(F13:F17)</f>
+        <v>11692000</v>
       </c>
     </row>
   </sheetData>

--- a/ข้อ2.xlsx
+++ b/ข้อ2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Product_AMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39A3B97-BCDD-4BCE-9567-309F7EDD1B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C3FF3F-D92A-4F2E-B3FC-26110CED61B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3E6D1783-A657-4040-8780-286ED815531D}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3E6D1783-A657-4040-8780-286ED815531D}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>

--- a/ข้อ2.xlsx
+++ b/ข้อ2.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Product_AMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C3FF3F-D92A-4F2E-B3FC-26110CED61B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01106E9-C9A8-41EC-B58C-020E95A502C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3E6D1783-A657-4040-8780-286ED815531D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3E6D1783-A657-4040-8780-286ED815531D}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
-    <sheet name="Plan2" sheetId="2" r:id="rId2"/>
-    <sheet name="Plan3" sheetId="3" r:id="rId3"/>
-    <sheet name="Plan4" sheetId="4" r:id="rId4"/>
-    <sheet name="EX" sheetId="5" r:id="rId5"/>
+    <sheet name="ข้อ2" sheetId="6" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId3"/>
+    <sheet name="Plan2" sheetId="2" r:id="rId4"/>
+    <sheet name="Plan3" sheetId="3" r:id="rId5"/>
+    <sheet name="Plan4" sheetId="4" r:id="rId6"/>
+    <sheet name="EX" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="37">
   <si>
     <t>เดือน</t>
   </si>
@@ -904,6 +906,426 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{548FC6A0-3574-4292-A735-E515DB9D0114}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.8984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>550</v>
+      </c>
+      <c r="C2">
+        <v>900</v>
+      </c>
+      <c r="D2">
+        <v>750</v>
+      </c>
+      <c r="E2">
+        <v>400</v>
+      </c>
+      <c r="G2">
+        <f>AVERAGE(B2:E2)</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <f>B2-B3</f>
+        <v>490</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:E4" si="0">C2+C3</f>
+        <v>900</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="F4">
+        <f>SUM(B4:E4)</f>
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>22</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <f>SUM(B5:E5)</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <f>$G$2</f>
+        <v>650</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:E7" si="1">$G$2</f>
+        <v>650</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>650</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <f>IF(B7&gt;$B$6, B7-$B$6, 0)</f>
+        <v>120</v>
+      </c>
+      <c r="C8">
+        <f>IF(C7&gt;B7, C7-B7, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="D8:E8" si="2">IF(D7&gt;C7, D7-C7, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <f>IF(B7&lt;$B$6, ABS(B7-$B$6), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f>IF(C7&lt;B7, ABS(C7-B7), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ref="D9:E9" si="3">IF(D7&lt;C7, ABS(D7-C7), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <f>B4+B3-B2</f>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ref="C10:E10" si="4">C4+C3-C2</f>
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11">
+        <f>IF(B7&gt;B4, 0, B4-B7)</f>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f>IF(C7&gt;C4, 0, C4-C7)</f>
+        <v>250</v>
+      </c>
+      <c r="D11">
+        <f>IF(D7&gt;D4, 0, D4-D7)</f>
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <f>IF(E7&gt;E4, 0, E4-E7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
+        <f>IF(B$7&gt;B$4,(B7-B4),0)</f>
+        <v>160</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ref="C12:E12" si="5">IF(C$7&gt;C$4,(C7-C4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="5"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13">
+        <f>(B3*0.5)*1600</f>
+        <v>48000</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:E13" si="6">(C3*0.5)*1600</f>
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>SUM(B13:E13)</f>
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <f>IF(B$7&gt;B$4,B$4*40*100,B$7*40*100)</f>
+        <v>1960000</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ref="C14:E14" si="7">IF(C$7&gt;C$4,C$4*40*100,C$7*40*100)</f>
+        <v>2600000</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="7"/>
+        <v>2600000</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="7"/>
+        <v>1600000</v>
+      </c>
+      <c r="F14">
+        <f>SUM(B14:E14)</f>
+        <v>8760000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <f>B11*100*55</f>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:E15" si="8">C11*100*55</f>
+        <v>1375000</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="8"/>
+        <v>550000</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" ref="F15:F16" si="9">SUM(B15:E15)</f>
+        <v>1925000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <f>B12*25*100</f>
+        <v>400000</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ref="C16:E16" si="10">C12*25*100</f>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="10"/>
+        <v>625000</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="9"/>
+        <v>1025000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <f>B8*1200</f>
+        <v>144000</v>
+      </c>
+      <c r="C17">
+        <f>C8*2000</f>
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <f>D8*2000</f>
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f>E8*2000</f>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f>SUM(B17:E17)</f>
+        <v>144000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <f>SUM(F13:F17)</f>
+        <v>11902000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A016C6-A540-42CB-86C8-26D6B5AD684D}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <f>_xlfn.NORM.DIST(11,12,1.6,TRUE)</f>
+        <v>0.26598552904870049</v>
+      </c>
+      <c r="B1">
+        <f>(A1*2)</f>
+        <v>0.53197105809740097</v>
+      </c>
+      <c r="C1">
+        <f>1-B1</f>
+        <v>0.46802894190259903</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <f>_xlfn.NORM.DIST(13,12,1.6,TRUE)</f>
+        <v>0.73401447095129946</v>
+      </c>
+      <c r="B2">
+        <f>A2-A1</f>
+        <v>0.46802894190259897</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>_xlfn.NORM.DIST(10,8.4,1.3,TRUE)</f>
+        <v>0.89079540669037915</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <f>_xlfn.NORM.INV(0.95,12,1.6)</f>
+        <v>14.631765803122354</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC06AD6-0B3E-480F-BEC6-CA0ADCB5C28A}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -1327,7 +1749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B94197-B93E-48D3-81D6-8F7F5DFC7FD7}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -1855,7 +2277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41F1413C-A459-49D4-A4EE-F26E20C7E4A0}">
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -2346,7 +2768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF99655-EC71-4C4C-808B-2045FF63058F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
